--- a/entertainment_forms/019_which_joker_portrayal_are_you--entertainment_forms.xlsx
+++ b/entertainment_forms/019_which_joker_portrayal_are_you--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_is_your_joker_portrayal</t>
+          <t>Which Joker Portrayal Are You</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_2</t>
+          <t>select_joker_portrayal_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>do_you_like_tragedy</t>
+          <t>Do You Prefer a Comedic or Dramatic Portrayal of the Joker?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_3</t>
+          <t>select_joker_portrayal_like</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>are_you_a_romantic</t>
+          <t>Can You Write a Joke Like the Joker?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_4</t>
+          <t>select_joker_portrayal_intensity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>do_you_like_tragedy</t>
+          <t>Do You Prefer a Light-Hearted or Darker Portrayal of the Joker?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_5</t>
+          <t>text_answer_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>are_you_a_clown</t>
+          <t>Report the Joker Portrayal You Prefer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>text_answer_1</t>
+          <t>select_joker_portrayal_like_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>report_the_joker_portrayal</t>
+          <t>Do You Like the Joker's Interactions with Other Characters?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_6</t>
+          <t>select_joker_portrayal_like_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>do_you_prefer_a_joker_portrayal</t>
+          <t>Can We Make the Joker's Portrayal More Relatable?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_7</t>
+          <t>select_joker_portrayal_like_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>which_joker_portrayal_is_your_favorite</t>
+          <t>Do You Want to See More of the Joker's Origin Story?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>text_answer_2</t>
+          <t>select_joker_portrayal_like_5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>describe_your_joker_portrayal</t>
+          <t>Can the Joker's Portrayal Be Too Intense for Your Taste?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_8</t>
+          <t>select_joker_portrayal_like_6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>can_you_write_a_joke</t>
+          <t>Do You Think the Joker's Personality Is Too One-Dimensional?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_9</t>
+          <t>select_joker_portrayal_like_7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>do_you_like_tragedy</t>
+          <t>Can We Add More Humor to the Joker's Character?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_10</t>
+          <t>text_answer_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>can_we_make_you_laugh</t>
+          <t>Tell Us a Joke Like the Joker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_11</t>
+          <t>select_joker_portrayal_like_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>do_we_make_your_joker_portrayal</t>
+          <t>Do You Like the Joker's Dialogue in Movies/TV Shows?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_12</t>
+          <t>select_joker_portrayal_like_9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>are_you_a_good_listener</t>
+          <t>Can We Add More Depth to the Joker's Character Development?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>text_answer_3</t>
+          <t>select_joker_portrayal_like_10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>report_the_joker_portrayal</t>
+          <t>Do You Like the Joker's Backstory in Movies/TV Shows?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_13</t>
+          <t>text_answer_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>can_we_make_you_laughter</t>
+          <t>Text Answer 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_14</t>
+          <t>select_joker_portrayal_like_11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>do_we_have_your_attention</t>
+          <t>Can We Make the Joker's Actions More Unpredictable?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_15</t>
+          <t>select_joker_portrayal_like_12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>do_we_have_your_laughter</t>
+          <t>Do You Like the Way the Joker's Personality Is Portrayed?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_16</t>
+          <t>select_joker_portrayal_like_13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>can_we_get_your_attention</t>
+          <t>Select Joker Portrayal Like 13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>text_answer_4</t>
+          <t>select_joker_portrayal_like_14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>tell_us_a_joke</t>
+          <t>Do You Like the Way the Joker's Backstory Is Portrayed?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>do_we_have_your_attention</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>do_we_make_your_joker_portrayal</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>do_we_have_your_laughter</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>do_we_get_your_attention</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>text_answer_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>report_the_joker_portrayal</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>comedic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Comedic</t>
         </is>
       </c>
     </row>
@@ -1148,53 +1033,53 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dramatic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dramatic</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_2_choices</t>
+          <t>select_joker_portrayal_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>comedic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Comedic</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_2_choices</t>
+          <t>select_joker_portrayal_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dramatic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dramatic</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_3_choices</t>
+          <t>select_joker_portrayal_like_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1096,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_3_choices</t>
+          <t>select_joker_portrayal_like_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,41 +1113,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_4_choices</t>
+          <t>select_joker_portrayal_intensity_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>light-hearted</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Light-Hearted</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_4_choices</t>
+          <t>select_joker_portrayal_intensity_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>darker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Darker</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_5_choices</t>
+          <t>select_joker_portrayal_like_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1164,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_5_choices</t>
+          <t>select_joker_portrayal_like_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1181,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_6_choices</t>
+          <t>select_joker_portrayal_like_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1198,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_6_choices</t>
+          <t>select_joker_portrayal_like_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1215,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_7_choices</t>
+          <t>select_joker_portrayal_like_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1232,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_7_choices</t>
+          <t>select_joker_portrayal_like_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1249,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_8_choices</t>
+          <t>select_joker_portrayal_like_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1266,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_8_choices</t>
+          <t>select_joker_portrayal_like_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_9_choices</t>
+          <t>select_joker_portrayal_like_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1300,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_9_choices</t>
+          <t>select_joker_portrayal_like_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1317,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_10_choices</t>
+          <t>select_joker_portrayal_like_7_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1334,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_10_choices</t>
+          <t>select_joker_portrayal_like_7_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1351,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_11_choices</t>
+          <t>select_joker_portrayal_like_8_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1368,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_11_choices</t>
+          <t>select_joker_portrayal_like_8_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1385,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_12_choices</t>
+          <t>select_joker_portrayal_like_9_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1402,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_12_choices</t>
+          <t>select_joker_portrayal_like_9_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_13_choices</t>
+          <t>select_joker_portrayal_like_10_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1436,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_13_choices</t>
+          <t>select_joker_portrayal_like_10_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1453,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_14_choices</t>
+          <t>select_joker_portrayal_like_11_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1470,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_14_choices</t>
+          <t>select_joker_portrayal_like_11_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1487,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_15_choices</t>
+          <t>select_joker_portrayal_like_12_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1504,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_15_choices</t>
+          <t>select_joker_portrayal_like_12_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1521,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_16_choices</t>
+          <t>select_joker_portrayal_like_13_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1538,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_16_choices</t>
+          <t>select_joker_portrayal_like_13_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1555,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_17_choices</t>
+          <t>select_joker_portrayal_like_14_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1572,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_joker_portrayal_17_choices</t>
+          <t>select_joker_portrayal_like_14_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1696,108 +1581,6 @@
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_18_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_18_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_19_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_19_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_20_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>select_joker_portrayal_20_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
